--- a/docentes/Ángel Martínez Noe Cristobal - Estadisticos 20221.xlsx
+++ b/docentes/Ángel Martínez Noe Cristobal - Estadisticos 20221.xlsx
@@ -609,16 +609,19 @@
         <v>41</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>41</v>
       </c>
-      <c r="E2">
-        <v>41</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>8.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -632,16 +635,19 @@
         <v>45</v>
       </c>
       <c r="D3">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H3">
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -655,16 +661,19 @@
         <v>32</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>32</v>
       </c>
-      <c r="E4">
-        <v>32</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -729,7 +738,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -746,16 +755,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G3">
-        <v>86.67</v>
+        <v>88.89</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -781,7 +790,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Ángel Martínez Noe Cristobal - Estadisticos 20221.xlsx
+++ b/docentes/Ángel Martínez Noe Cristobal - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -79,16 +79,25 @@
     <t>JUSTO</t>
   </si>
   <si>
+    <t>MORENO</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
     <t>NEGRETE</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
     <t>MARIA MICHELLE</t>
+  </si>
+  <si>
+    <t>NAHOMY</t>
   </si>
   <si>
     <t>DIEGO EMILIO</t>
@@ -635,16 +644,16 @@
         <v>45</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G3">
-        <v>80</v>
+        <v>86.67</v>
       </c>
       <c r="H3">
         <v>7.1</v>
@@ -755,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3">
-        <v>88.89</v>
+        <v>86.67</v>
       </c>
       <c r="H3">
         <v>7.4</v>
@@ -800,7 +809,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -838,10 +847,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -855,16 +864,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920323</v>
+        <v>19330051920208</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -873,6 +882,29 @@
         <v>11</v>
       </c>
       <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920323</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ángel Martínez Noe Cristobal - Estadisticos 20221.xlsx
+++ b/docentes/Ángel Martínez Noe Cristobal - Estadisticos 20221.xlsx
@@ -76,13 +76,16 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>JUSTO</t>
   </si>
   <si>
     <t>MORENO</t>
   </si>
   <si>
-    <t>ROMERO</t>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>NEGRETE</t>
@@ -91,16 +94,13 @@
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>DIEGO EMILIO</t>
   </si>
   <si>
     <t>MARIA MICHELLE</t>
   </si>
   <si>
     <t>NAHOMY</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
   </si>
 </sst>
 </file>
@@ -841,7 +841,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920305</v>
+        <v>21330051920323</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
@@ -859,12 +859,12 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920208</v>
+        <v>21330051920305</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920323</v>
+        <v>19330051920208</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>

--- a/docentes/Ángel Martínez Noe Cristobal - Estadisticos 20221.xlsx
+++ b/docentes/Ángel Martínez Noe Cristobal - Estadisticos 20221.xlsx
@@ -738,16 +738,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>97.56</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -799,7 +799,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Ángel Martínez Noe Cristobal - Estadisticos 20221.xlsx
+++ b/docentes/Ángel Martínez Noe Cristobal - Estadisticos 20221.xlsx
@@ -79,28 +79,28 @@
     <t>ROMERO</t>
   </si>
   <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
     <t>JUSTO</t>
   </si>
   <si>
-    <t>MORENO</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
     <t>NEGRETE</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
     <t>DIEGO EMILIO</t>
   </si>
   <si>
+    <t>KARINA YOSELIN</t>
+  </si>
+  <si>
     <t>MARIA MICHELLE</t>
-  </si>
-  <si>
-    <t>NAHOMY</t>
   </si>
 </sst>
 </file>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G3">
-        <v>86.67</v>
+        <v>84.44</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -864,7 +864,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920305</v>
+        <v>21330051920328</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
@@ -882,12 +882,12 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920208</v>
+        <v>21330051920305</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>

--- a/docentes/Ángel Martínez Noe Cristobal - Estadisticos 20221.xlsx
+++ b/docentes/Ángel Martínez Noe Cristobal - Estadisticos 20221.xlsx
@@ -76,31 +76,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>JUSTO</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>NEGRETE</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>NEGRETE</t>
+    <t>KARINA YOSELIN</t>
+  </si>
+  <si>
+    <t>MARIA MICHELLE</t>
   </si>
   <si>
     <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>KARINA YOSELIN</t>
-  </si>
-  <si>
-    <t>MARIA MICHELLE</t>
   </si>
 </sst>
 </file>
@@ -841,7 +841,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920323</v>
+        <v>21330051920328</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
@@ -864,7 +864,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920328</v>
+        <v>21330051920305</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
@@ -882,12 +882,12 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920305</v>
+        <v>21330051920323</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
